--- a/Listing/RWS05.xlsx
+++ b/Listing/RWS05.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="348" uniqueCount="133">
   <si>
     <t/>
   </si>
@@ -196,6 +196,18 @@
     <t>CORNETTO CHO BROWNIE</t>
   </si>
   <si>
+    <t>20141545</t>
+  </si>
+  <si>
+    <t>WALLS CLP STWPINE100</t>
+  </si>
+  <si>
+    <t>20141544</t>
+  </si>
+  <si>
+    <t>WALLS CLP PEACHMG100</t>
+  </si>
+  <si>
     <t>20125168</t>
   </si>
   <si>
@@ -242,6 +254,18 @@
   </si>
   <si>
     <t>WALLS FEAST MAX CHO</t>
+  </si>
+  <si>
+    <t>20141200</t>
+  </si>
+  <si>
+    <t>WALLS BALL STRW GUAV</t>
+  </si>
+  <si>
+    <t>20141201</t>
+  </si>
+  <si>
+    <t>WALLS BALL GRAPE</t>
   </si>
   <si>
     <t>20129821</t>
@@ -778,7 +802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1260,10 +1284,10 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>19</v>
@@ -1280,13 +1304,13 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1303,10 +1327,10 @@
         <v>14</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1323,7 +1347,7 @@
         <v>14</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>5</v>
@@ -1343,10 +1367,10 @@
         <v>14</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1363,10 +1387,10 @@
         <v>14</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1383,7 +1407,7 @@
         <v>14</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="F30" s="1" t="s">
         <v>19</v>
@@ -1403,7 +1427,7 @@
         <v>14</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="F31" s="1" t="s">
         <v>19</v>
@@ -1420,10 +1444,10 @@
         <v>3</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>19</v>
@@ -1440,13 +1464,13 @@
         <v>3</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1460,13 +1484,13 @@
         <v>3</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1480,10 +1504,10 @@
         <v>3</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>19</v>
@@ -1503,7 +1527,7 @@
         <v>24</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>19</v>
@@ -1523,10 +1547,10 @@
         <v>24</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -1540,10 +1564,10 @@
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>5</v>
@@ -1560,10 +1584,10 @@
         <v>3</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>19</v>
@@ -1580,10 +1604,10 @@
         <v>3</v>
       </c>
       <c r="D40" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E40" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>19</v>
@@ -1600,13 +1624,13 @@
         <v>3</v>
       </c>
       <c r="D41" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E41" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E41" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F41" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -1620,13 +1644,13 @@
         <v>3</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -1640,10 +1664,10 @@
         <v>3</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>19</v>
@@ -1660,10 +1684,10 @@
         <v>3</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>19</v>
@@ -1683,10 +1707,10 @@
         <v>29</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -1703,10 +1727,10 @@
         <v>29</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -1720,13 +1744,13 @@
         <v>3</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1740,13 +1764,13 @@
         <v>3</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1760,13 +1784,13 @@
         <v>3</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>14</v>
+        <v>41</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -1780,13 +1804,13 @@
         <v>3</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -1803,10 +1827,10 @@
         <v>32</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -1823,10 +1847,10 @@
         <v>32</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -1843,10 +1867,10 @@
         <v>32</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -1860,13 +1884,93 @@
         <v>3</v>
       </c>
       <c r="D54" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="B55" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F55" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="E58" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F54" s="1" t="s">
-        <v>124</v>
+      <c r="F58" s="1" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
